--- a/02_Pipeline/outputs/filter_view.xlsx
+++ b/02_Pipeline/outputs/filter_view.xlsx
@@ -467,7 +467,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Here I Teached</t>
+          <t>As a lecturer, I gave students insights into the field of general molecular biology.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Through academic research, I learned to explore complex biological systems with creativity and persistence. Investigating microorganismic interactions sharpened my skills in problem-solving, experimental design and data analysis  - insights that I now apply beyond the lab to innovation and sustainability.</t>
+          <t>Explored a complex phototropic system which is used for sustainable bioremediation (water cleaning) through academic biotechnological research. Sharpened skills in problem-solving, experimental design and data analysis. Published results in peer-reviewed journals.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>My journey into data science taught me how to translate raw data into actionable insights. From statistical modeling to visualization, I learned how to use various tools. Combining technical skills with storytelling allows me to uncover patterns, support decisions and communicate results effectively.</t>
+          <t>Processed and analyzed large biological datasets. Designed reproducible data workflows and scientific models using Python (statistical analysis, multivariate techniques). Published results in peer-reviewed journals.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -534,7 +534,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Here i learned</t>
+          <t>After graduation, I specialist into the field of biology. Explored the beauty and detailness of animals, plants and microorganisms.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Working with SMEs and research institutions taught me how to navigate funding landscapes and bring together different partners to work towards shared goals. I developed strategic innovation skills, learned to transform ideas into structured projects and shaped R&amp;D networks that drive progressive technologies.</t>
+          <t>Advised clients on innovation strategies and technology-driven projects, including AI and data-related applications (from idea framing to successful funding acquisition). Collaborated with cross-functional stake-holders across industry &amp; research.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -576,7 +576,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Here I developed</t>
+          <t>As a hobby, I create games focusing on model creation (Blender) and engine coding (Unity).</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -616,11 +616,7 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Here I don't know</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>

--- a/02_Pipeline/outputs/filter_view.xlsx
+++ b/02_Pipeline/outputs/filter_view.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Explored a complex phototropic system which is used for sustainable bioremediation (water cleaning) through academic biotechnological research. Sharpened skills in problem-solving, experimental design and data analysis. Published results in peer-reviewed journals.</t>
+          <t>My research journey led me to investigate a complex phototropic system designed for sustainable bioremediation, specifically for water cleaning. Through academic biotechnological research, I sharpened my skills in problem-solving, experimental design and data analysis. Finally, I published my findings in peer-reviewed journals to contribute to the broader scientific community.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -513,12 +513,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Processed and analyzed large biological datasets. Designed reproducible data workflows and scientific models using Python (statistical analysis, multivariate techniques). Published results in peer-reviewed journals.</t>
+          <t>I processed and analyzed large-scale biological datasets to uncover meaningful patterns. I designed reproducible data workflows and developed scientific models using Python, employing statistical analysis and multivariate techniques. Finally, I published my findings in peer-reviewed journals to contribute to the broader scientific community.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>#DataScience #Insights #Visualization</t>
+          <t>#DataAnalysis #Python #DataVisualization</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>After graduation, I specialist into the field of biology. Explored the beauty and detailness of animals, plants and microorganisms.</t>
+          <t>Following my graduation, I specialized in the field of biology, where I explored the intricate beauty and detailed mechanisms of animals, plants, and microorganisms. This focus allowed me to delve deep into the natural world while building a robust foundation in life sciences.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Advised clients on innovation strategies and technology-driven projects, including AI and data-related applications (from idea framing to successful funding acquisition). Collaborated with cross-functional stake-holders across industry &amp; research.</t>
+          <t>I advise clients on innovation strategies and technology-driven projects, including AI and data-related applications. My role spans the entire lifecycle from collaboratively framing initial ideas into successfully funded projects. In this capacity, I collaborate closely with cross-functional stakeholders across both industry and research sectors to help bridge the gap between theoretical potential and practical implementation.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>I thrive at the intersection of science, innovation and data. My path taught me to adapt quickly, communicate effectively and create impact in diverse contexts. Along the way, I learned to shape projects strategically and make complex information accessible through clear visualization and storytelling.</t>
+          <t>Following my graduation, I specialized in the field of biology, where I explored the beauty and detailed mechanisms of animals, plants and microorganisms.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">

--- a/02_Pipeline/outputs/filter_view.xlsx
+++ b/02_Pipeline/outputs/filter_view.xlsx
@@ -534,7 +534,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Following my graduation, I specialized in the field of biology, where I explored the intricate beauty and detailed mechanisms of animals, plants, and microorganisms. This focus allowed me to delve deep into the natural world while building a robust foundation in life sciences.</t>
+          <t>I thrive at the intersection of science, innovation, and data. My path taught me to adapt quickly, communicate effectively and create serious impact across diverse contexts. Along my way, I have learned to shape projects strategically and transform complex information into accessible insights through clear visualization and compelling storytelling.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>

--- a/02_Pipeline/outputs/filter_view.xlsx
+++ b/02_Pipeline/outputs/filter_view.xlsx
@@ -534,7 +534,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>I thrive at the intersection of science, innovation, and data. My path taught me to adapt quickly, communicate effectively and create serious impact across diverse contexts. Along my way, I have learned to shape projects strategically and transform complex information into accessible insights through clear visualization and compelling storytelling.</t>
+          <t>Following my graduation, I specialized in the field of biology, where I explored the beauty and detailed mechanisms of animals, plants and microorganisms.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Following my graduation, I specialized in the field of biology, where I explored the beauty and detailed mechanisms of animals, plants and microorganisms.</t>
+          <t>I thrive at the intersection of science, innovation and data. My path taught me to adapt quickly, communicate effectively and create serious impact across diverse contexts. Along my way, I have learned to shape projects strategically and transform complex information into accessible insights through clear visualization and compelling storytelling.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">

--- a/02_Pipeline/outputs/filter_view.xlsx
+++ b/02_Pipeline/outputs/filter_view.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>My research journey led me to investigate a complex phototropic system designed for sustainable bioremediation, specifically for water cleaning. Through academic biotechnological research, I sharpened my skills in problem-solving, experimental design and data analysis. Finally, I published my findings in peer-reviewed journals to contribute to the broader scientific community.</t>
+          <t>My research journey led me to investigate a complex phototropic system designed for sustainable bioremediation, specifically for water cleaning. Through academic biotechnological research, I sharpened my skills in problem-solving, experimental design and data analysis. Finally, I published my findings in peer-reviewed journals.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>I processed and analyzed large-scale biological datasets to uncover meaningful patterns. I designed reproducible data workflows and developed scientific models using Python, employing statistical analysis and multivariate techniques. Finally, I published my findings in peer-reviewed journals to contribute to the broader scientific community.</t>
+          <t>I processed and analyzed large-scale biological datasets (metagenomic sequencing data) to uncover meaningful patterns. I designed reproducible data workflows and developed scientific models using Python, employing statistical analysis and multivariate techniques. Finally, I published my findings in peer-reviewed journals.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>I advise clients on innovation strategies and technology-driven projects, including AI and data-related applications. My role spans the entire lifecycle from collaboratively framing initial ideas into successfully funded projects. In this capacity, I collaborate closely with cross-functional stakeholders across both industry and research sectors to help bridge the gap between theoretical potential and practical implementation.</t>
+          <t>I advise clients on innovation strategies and technology-driven projects, including AI and data-related applications. My role spans the entire lifecycle from collaboratively framing initial ideas into successfully funded projects. In this capacity, I collaborate closely with cross-functional stakeholders across both industry and research sectors.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
